--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -22,7 +22,11 @@
     <sheet name="13 Break-even" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="14 Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="15 Alternative A" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16 Summary" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17 Proposed tariff" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="18 Architectures" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="19 Core Plan" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="20 Price scenarios" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="16 Summary" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3274,12 +3278,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3292,169 +3301,1163 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>16 Summary</t>
+          <t>17 Proposed tariff</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>The decade in one view, expected case.</t>
+          <t>PROPOSED / MODELLED. Not adopted. The published tariff remains $19,000.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Measure</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ten-year</t>
+          <t>CEFR</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Year 10</t>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Tutored</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Exec Core</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Exec Premium</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Exec Bespoke</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Gross tuition</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>91500589</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>17117317</v>
+          <t>ECIC</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>English Communication Introductory Certificate</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>3700</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>11250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Refunds</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>2013012</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>376581</v>
+          <t>HCIC</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Higher Communication Introductory Certificate</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>7100</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>12500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Fee remission (scholarships)</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>4575029</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>855866</v>
+          <t>CAEC</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Certificate in Applied English Communication</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>2700</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>8350</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>14200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Net tuition</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>84912545</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>15884870</v>
+          <t>HCAEC</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Higher Certificate in Applied English Communication</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>5750</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>9850</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>16250</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Total cost</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>64880256</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>10987757</v>
+          <t>ACEC</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Certificate in English Communication</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>19200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>WEPC</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>WorldWide English Proficiency Certificate</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>14500</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>22600</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>COMPLETE A1–C2 PATHWAY</t>
+        </is>
+      </c>
+      <c r="D13" s="15">
+        <f>SUM(D7:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
+        <f>SUM(E7:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>SUM(F7:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="15">
+        <f>SUM(G7:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="15">
+        <f>SUM(H7:H12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Per academic hour (1,200 hours)</t>
+        </is>
+      </c>
+      <c r="D14" s="7">
+        <f>D13/1200</f>
+        <v/>
+      </c>
+      <c r="E14" s="7">
+        <f>E13/1200</f>
+        <v/>
+      </c>
+      <c r="F14" s="7">
+        <f>F13/1200</f>
+        <v/>
+      </c>
+      <c r="G14" s="7">
+        <f>G13/1200</f>
+        <v/>
+      </c>
+      <c r="H14" s="7">
+        <f>H13/1200</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorldWide English College — London Campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>18 Architectures</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Three architectures through one demand model, one cost model, one capacity gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Ten-year revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Ten-year surplus</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Year-10 revenue</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Year-10 active</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Awards conferred</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Closing reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Brief A — $7,400 / $14,800</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>58074016</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>2943992</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>9938254</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>5839</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>7589</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>2994359</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Adopted flat $19,000</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>57783185</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>17202006</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>10034862</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>2964</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>3799</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>10881207</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Proposed portfolio</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>61565430</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>14141690</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>10510847</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>4845</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>6306</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>9163516</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorldWide English College — London Campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>19 Core Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Management's recommended execution case under the proposed architecture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>New learners</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Instructors</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
           <t>Surplus</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v>20032291</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>4897113</v>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Cumulative surplus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>342745</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>116253</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>68041</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>785714</v>
+      </c>
+      <c r="J7" s="15">
+        <f>F7-G7-H7-I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="9">
+        <f>IF(F7=0,0,J7/F7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="15">
+        <f>J7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>291</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>553</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1201227</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>407436</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>238464</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>951429</v>
+      </c>
+      <c r="J8" s="15">
+        <f>F8-G8-H8-I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="9">
+        <f>IF(F8=0,0,J8/F8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="15">
+        <f>L7+J8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>530</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>2184018</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>740782</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>433565</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1117143</v>
+      </c>
+      <c r="J9" s="15">
+        <f>F9-G9-H9-I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="9">
+        <f>IF(F9=0,0,J9/F9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="15">
+        <f>L8+J9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>969</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1841</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>3993934</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>1354674</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>792865</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>1282857</v>
+      </c>
+      <c r="J10" s="15">
+        <f>F10-G10-H10-I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="9">
+        <f>IF(F10=0,0,J10/F10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="15">
+        <f>L9+J10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>2031</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>1447</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>2749</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>5965241</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>2023308</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>1184203</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>1448571</v>
+      </c>
+      <c r="J11" s="15">
+        <f>F11-G11-H11-I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="9">
+        <f>IF(F11=0,0,J11/F11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="15">
+        <f>L10+J11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>2032</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1831</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3479</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>7546091</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>2559505</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>1498029</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1614286</v>
+      </c>
+      <c r="J12" s="15">
+        <f>F12-G12-H12-I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="9">
+        <f>IF(F12=0,0,J12/F12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="15">
+        <f>L11+J12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Levels delivered</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>44392</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>8341.9</v>
+      <c r="A13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>2033</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>2183</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>4148</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>8996825</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>3051569</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>1786025</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="J13" s="15">
+        <f>F13-G13-H13-I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="9">
+        <f>IF(F13=0,0,J13/F13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="15">
+        <f>L12+J13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Awards conferred</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>44392</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>8341.9</v>
+      <c r="A14" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>2034</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>2502</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>4754</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>10313655</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>3498215</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>2047438</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="J14" s="15">
+        <f>F14-G14-H14-I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="9">
+        <f>IF(F14=0,0,J14/F14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="15">
+        <f>L13+J14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Active learners (peak / Y10)</t>
-        </is>
+      <c r="A15" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="8" t="n">
-        <v>2071</v>
+        <v>2035</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2071</v>
+        <v>2550</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>4845</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>10510847</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>3565100</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>2086584</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="J15" s="15">
+        <f>F15-G15-H15-I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="9">
+        <f>IF(F15=0,0,J15/F15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="15">
+        <f>L14+J15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Instructors</t>
-        </is>
+      <c r="A16" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>2036</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>75</v>
+        <v>2550</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>4845</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>10510847</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>3565100</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>2086584</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="J16" s="15">
+        <f>F16-G16-H16-I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="9">
+        <f>IF(F16=0,0,J16/F16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="15">
+        <f>L15+J16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Closing reserve</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>12604510</v>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>TEN YEARS</t>
+        </is>
+      </c>
+      <c r="F17" s="15">
+        <f>SUM(F7:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="15">
+        <f>SUM(G7:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="15">
+        <f>SUM(H7:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="15">
+        <f>SUM(I7:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="15">
+        <f>SUM(J7:J16)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorldWide English College — London Campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>20 Price scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Conservative is not a haircut on Core: weaker continuation, narrower reach, dearer acquisition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Ten-year revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Ten-year surplus</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Year-10 revenue</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Year-10 new</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Year-10 active</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Awards</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>35791425</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>-1843882</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>6228939</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1887</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>3585</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Core Management Plan</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>61565430</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>14141690</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>10510847</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>2550</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>4845</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>6306</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>High Growth</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>95500442</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>35110823</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>16045849</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>3264</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>6202</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>12627</v>
       </c>
     </row>
   </sheetData>
@@ -3796,6 +4799,200 @@
         <is>
           <t>Six levels at $3,166.67 sum to $19,000.02. The College charges $19,000 and waives two cents — see data/tuition.json § _rounding.</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorldWide English College — London Campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>16 Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>The decade in one view, expected case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Ten-year</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Year 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Gross tuition</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>91500589</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>17117317</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Refunds</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>2013012</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>376581</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Fee remission (scholarships)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>4575029</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>855866</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net tuition</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>84912545</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>15884870</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Total cost</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>64880256</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>10987757</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Surplus</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>20032291</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>4897113</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Levels delivered</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>44392</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>8341.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Awards conferred</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>44392</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>8341.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Active learners (peak / Y10)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>2071</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Instructors</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Closing reserve</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>12604510</v>
       </c>
     </row>
   </sheetData>

--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -26,7 +26,9 @@
     <sheet name="18 Architectures" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="19 Core Plan" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="20 Price scenarios" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="16 Summary" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="21 Market evidence" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="22 Teaching frontier" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="16 Summary" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3371,19 +3373,19 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>2050</v>
+        <v>1750</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>3700</v>
+        <v>3100</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>6200</v>
+        <v>4950</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>11250</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="8">
@@ -3403,19 +3405,19 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>2300</v>
+        <v>1950</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>7100</v>
+        <v>5650</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>12500</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="9">
@@ -3435,19 +3437,19 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1350</v>
+        <v>1450</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>2700</v>
+        <v>2250</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>4900</v>
+        <v>4050</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>8350</v>
+        <v>6650</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>14200</v>
+        <v>11250</v>
       </c>
     </row>
     <row r="10">
@@ -3467,19 +3469,19 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3150</v>
+        <v>2650</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>5750</v>
+        <v>4750</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>9850</v>
+        <v>7800</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>16250</v>
+        <v>12850</v>
       </c>
     </row>
     <row r="11">
@@ -3499,19 +3501,19 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>1750</v>
+        <v>1850</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3800</v>
+        <v>3150</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>7000</v>
+        <v>5750</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>12000</v>
+        <v>9500</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>19200</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="12">
@@ -3531,19 +3533,19 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>4500</v>
+        <v>3750</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>8450</v>
+        <v>6850</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>14500</v>
+        <v>11450</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>22600</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="13">
@@ -3688,22 +3690,22 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>58074016</v>
+        <v>29059990</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>2943992</v>
+        <v>-3221563</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>9938254</v>
+        <v>5193804</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>5839</v>
+        <v>1917</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>7589</v>
+        <v>19863</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>2994359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3713,22 +3715,22 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>57783185</v>
+        <v>27268930</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>17202006</v>
+        <v>4682740</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>10034862</v>
+        <v>4999314</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>2964</v>
+        <v>974</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3799</v>
+        <v>9835</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>10881207</v>
+        <v>3443477</v>
       </c>
     </row>
     <row r="9">
@@ -3738,22 +3740,22 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>61565430</v>
+        <v>37744623</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>14141690</v>
+        <v>2274765</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>10510847</v>
+        <v>6667802</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>4845</v>
+        <v>2648</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>6306</v>
+        <v>27760</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>9163516</v>
+        <v>2225710</v>
       </c>
     </row>
   </sheetData>
@@ -3767,7 +3769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3782,6 +3784,9 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3833,35 +3838,50 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Gross fees</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
+          <t>Refunds</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Net tuition</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
           <t>Delivery</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>Surplus</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>Margin</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Cumulative surplus</t>
         </is>
@@ -3875,36 +3895,46 @@
         <v>2027</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>342745</v>
+        <v>142300</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>116253</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>68041</v>
+        <v>3131</v>
+      </c>
+      <c r="H7" s="10">
+        <f>F7-G7</f>
+        <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>785714</v>
-      </c>
-      <c r="J7" s="15">
-        <f>F7-G7-H7-I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="9">
-        <f>IF(F7=0,0,J7/F7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="15">
-        <f>J7</f>
+        <v>61004</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>58568</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>363820</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>7654</v>
+      </c>
+      <c r="M7" s="15">
+        <f>H7-I7-J7-K7-L7</f>
+        <v/>
+      </c>
+      <c r="N7" s="9">
+        <f>IF(F7=0,0,M7/F7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="15">
+        <f>M7</f>
         <v/>
       </c>
     </row>
@@ -3916,36 +3946,46 @@
         <v>2028</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>553</v>
+        <v>258</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1201227</v>
+        <v>574259</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>407436</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>238464</v>
+        <v>12634</v>
+      </c>
+      <c r="H8" s="10">
+        <f>F8-G8</f>
+        <v/>
       </c>
       <c r="I8" s="10" t="n">
-        <v>951429</v>
-      </c>
-      <c r="J8" s="15">
-        <f>F8-G8-H8-I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="9">
-        <f>IF(F8=0,0,J8/F8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="15">
-        <f>L7+J8</f>
+        <v>246074</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>205434</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>30889</v>
+      </c>
+      <c r="M8" s="15">
+        <f>H8-I8-J8-K8-L8</f>
+        <v/>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(F8=0,0,M8/F8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="15">
+        <f>O7+M8</f>
         <v/>
       </c>
     </row>
@@ -3957,36 +3997,46 @@
         <v>2029</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>530</v>
+        <v>438</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>1007</v>
+        <v>501</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>2184018</v>
+        <v>1173613</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>740782</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>433565</v>
+        <v>25819</v>
+      </c>
+      <c r="H9" s="10">
+        <f>F9-G9</f>
+        <v/>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1117143</v>
-      </c>
-      <c r="J9" s="15">
-        <f>F9-G9-H9-I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="9">
-        <f>IF(F9=0,0,J9/F9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="15">
-        <f>L8+J9</f>
+        <v>502740</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>374579</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>63129</v>
+      </c>
+      <c r="M9" s="15">
+        <f>H9-I9-J9-K9-L9</f>
+        <v/>
+      </c>
+      <c r="N9" s="9">
+        <f>IF(F9=0,0,M9/F9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="15">
+        <f>O8+M9</f>
         <v/>
       </c>
     </row>
@@ -3998,36 +4048,46 @@
         <v>2030</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>969</v>
+        <v>895</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1841</v>
+        <v>1009</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3993934</v>
+        <v>2342068</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1354674</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>792865</v>
+        <v>51525</v>
+      </c>
+      <c r="H10" s="10">
+        <f>F10-G10</f>
+        <v/>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1282857</v>
-      </c>
-      <c r="J10" s="15">
-        <f>F10-G10-H10-I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="9">
-        <f>IF(F10=0,0,J10/F10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="15">
-        <f>L9+J10</f>
+        <v>1003337</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>766194</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>125980</v>
+      </c>
+      <c r="M10" s="15">
+        <f>H10-I10-J10-K10-L10</f>
+        <v/>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(F10=0,0,M10/F10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="15">
+        <f>O9+M10</f>
         <v/>
       </c>
     </row>
@@ -4039,36 +4099,46 @@
         <v>2031</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1447</v>
+        <v>1217</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>2749</v>
+        <v>1451</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5965241</v>
+        <v>3512020</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>2023308</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>1184203</v>
+        <v>77264</v>
+      </c>
+      <c r="H11" s="10">
+        <f>F11-G11</f>
+        <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1448571</v>
-      </c>
-      <c r="J11" s="15">
-        <f>F11-G11-H11-I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="9">
-        <f>IF(F11=0,0,J11/F11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="15">
-        <f>L10+J11</f>
+        <v>1504156</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>1040969</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>188912</v>
+      </c>
+      <c r="M11" s="15">
+        <f>H11-I11-J11-K11-L11</f>
+        <v/>
+      </c>
+      <c r="N11" s="9">
+        <f>IF(F11=0,0,M11/F11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="15">
+        <f>O10+M11</f>
         <v/>
       </c>
     </row>
@@ -4080,36 +4150,46 @@
         <v>2032</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1831</v>
+        <v>1560</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3479</v>
+        <v>1878</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7546091</v>
+        <v>4578989</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2559505</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>1498029</v>
+        <v>100738</v>
+      </c>
+      <c r="H12" s="10">
+        <f>F12-G12</f>
+        <v/>
       </c>
       <c r="I12" s="10" t="n">
-        <v>1614286</v>
-      </c>
-      <c r="J12" s="15">
-        <f>F12-G12-H12-I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="9">
-        <f>IF(F12=0,0,J12/F12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="15">
-        <f>L11+J12</f>
+        <v>1961047</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>1335045</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>246304</v>
+      </c>
+      <c r="M12" s="15">
+        <f>H12-I12-J12-K12-L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="9">
+        <f>IF(F12=0,0,M12/F12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="15">
+        <f>O11+M12</f>
         <v/>
       </c>
     </row>
@@ -4121,36 +4201,46 @@
         <v>2033</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2183</v>
+        <v>1892</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>4148</v>
+        <v>2300</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>8996825</v>
+        <v>5645475</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>3051569</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>1786025</v>
+        <v>124200</v>
+      </c>
+      <c r="H13" s="10">
+        <f>F13-G13</f>
+        <v/>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1780000</v>
-      </c>
-      <c r="J13" s="15">
-        <f>F13-G13-H13-I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="9">
-        <f>IF(F13=0,0,J13/F13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="15">
-        <f>L12+J13</f>
+        <v>2417694</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>1618733</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>303670</v>
+      </c>
+      <c r="M13" s="15">
+        <f>H13-I13-J13-K13-L13</f>
+        <v/>
+      </c>
+      <c r="N13" s="9">
+        <f>IF(F13=0,0,M13/F13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="15">
+        <f>O12+M13</f>
         <v/>
       </c>
     </row>
@@ -4162,36 +4252,46 @@
         <v>2034</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2502</v>
+        <v>2099</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4754</v>
+        <v>2594</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>10313655</v>
+        <v>6440295</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>3498215</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>2047438</v>
+        <v>141686</v>
+      </c>
+      <c r="H14" s="10">
+        <f>F14-G14</f>
+        <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1780000</v>
-      </c>
-      <c r="J14" s="15">
-        <f>F14-G14-H14-I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="9">
-        <f>IF(F14=0,0,J14/F14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="15">
-        <f>L13+J14</f>
+        <v>2757896</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>1796092</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>346423</v>
+      </c>
+      <c r="M14" s="15">
+        <f>H14-I14-J14-K14-L14</f>
+        <v/>
+      </c>
+      <c r="N14" s="9">
+        <f>IF(F14=0,0,M14/F14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="15">
+        <f>O13+M14</f>
         <v/>
       </c>
     </row>
@@ -4203,36 +4303,46 @@
         <v>2035</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2550</v>
+        <v>2099</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>4845</v>
+        <v>2648</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>10510847</v>
+        <v>6667802</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>3565100</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>2086584</v>
+        <v>146692</v>
+      </c>
+      <c r="H15" s="10">
+        <f>F15-G15</f>
+        <v/>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1780000</v>
-      </c>
-      <c r="J15" s="15">
-        <f>F15-G15-H15-I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="9">
-        <f>IF(F15=0,0,J15/F15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="15">
-        <f>L14+J15</f>
+        <v>2855093</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>1796092</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>358661</v>
+      </c>
+      <c r="M15" s="15">
+        <f>H15-I15-J15-K15-L15</f>
+        <v/>
+      </c>
+      <c r="N15" s="9">
+        <f>IF(F15=0,0,M15/F15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="15">
+        <f>O14+M15</f>
         <v/>
       </c>
     </row>
@@ -4244,36 +4354,46 @@
         <v>2036</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2550</v>
+        <v>2099</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>4845</v>
+        <v>2648</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>10510847</v>
+        <v>6667802</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>3565100</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>2086584</v>
+        <v>146692</v>
+      </c>
+      <c r="H16" s="10">
+        <f>F16-G16</f>
+        <v/>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1780000</v>
-      </c>
-      <c r="J16" s="15">
-        <f>F16-G16-H16-I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="9">
-        <f>IF(F16=0,0,J16/F16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="15">
-        <f>L15+J16</f>
+        <v>2855093</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>1796092</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>588160</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>358661</v>
+      </c>
+      <c r="M16" s="15">
+        <f>H16-I16-J16-K16-L16</f>
+        <v/>
+      </c>
+      <c r="N16" s="9">
+        <f>IF(F16=0,0,M16/F16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="15">
+        <f>O15+M16</f>
         <v/>
       </c>
     </row>
@@ -4301,6 +4421,18 @@
       </c>
       <c r="J17" s="15">
         <f>SUM(J7:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="15">
+        <f>SUM(K7:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="15">
+        <f>SUM(L7:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="15">
+        <f>SUM(M7:M16)</f>
         <v/>
       </c>
     </row>
@@ -4392,22 +4524,22 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>35791425</v>
+        <v>22581373</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>-1843882</v>
+        <v>-4423959</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>6228939</v>
+        <v>3970149</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1887</v>
+        <v>1553</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>3585</v>
+        <v>1830</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>2417</v>
+        <v>17269</v>
       </c>
     </row>
     <row r="8">
@@ -4417,22 +4549,22 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>61565430</v>
+        <v>37744623</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>14141690</v>
+        <v>2274765</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>10510847</v>
+        <v>6667802</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>2550</v>
+        <v>2099</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>4845</v>
+        <v>2648</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>6306</v>
+        <v>27760</v>
       </c>
     </row>
     <row r="9">
@@ -4442,22 +4574,22 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>95500442</v>
+        <v>57305109</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>35110823</v>
+        <v>10792427</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>16045849</v>
+        <v>10143762</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>3264</v>
+        <v>2687</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>6202</v>
+        <v>3597</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>12627</v>
+        <v>40901</v>
       </c>
     </row>
   </sheetData>
@@ -4807,6 +4939,1385 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorldWide English College — London Campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>21 Market evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Published prices, converted. Gathered 2026-09-19. USD conversions use approximate mid-market rates at the research date: SAR 3.75, AED 3.67, GBP 0.79, NGN 1540. Local-currency figures are authoritative; USD is indicative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>What it buys</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Local price</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Per contact hour</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia and the Gulf</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>British Council Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Adult English, modular. 5 levels A2–C1. Module = 6 lessons of 90 minutes.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SAR 7,992.50 incl. VAT</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>2131</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>https://saudiarabia.britishcouncil.org/en/english/courses-adults/classes/programmes-pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>British Council Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Adult English, 40 credits</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SAR 6,037.50 incl. VAT</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1610</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>https://saudiarabia.britishcouncil.org/en/english/courses-adults/classes/programmes-pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>British Council Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Adult English, 20 credits</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SAR 3,795 incl. VAT</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>https://saudiarabia.britishcouncil.org/en/english/courses-adults/classes/programmes-pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>British Council Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>IELTS test fee (Academic / General Training)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SAR 1,636 incl. VAT</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>436</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>https://ieltsbiz.com/ielts-fees/saudi-arabia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>British Council United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>IELTS preparation course</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>AED 2,950</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>804</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>https://www.britishcouncil.ae/en/english/adults/ielts-preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Berlitz UAE</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>English group classes (promotional)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>AED 2,900</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>790</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.berlitz.com/en-ae/blog/english-group-classes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Dubai market survey</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Intensive English programmes, 2–3 months</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>AED 4,000 – 8,000+</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>1,090 – 2,180+</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>https://expressenglish.ae/english-course-fees-dubai-complete-price-guide/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Wall Street English Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>English course packages</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>NOT PUBLISHED</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>https://wallstreetenglish.edu.sa/en/prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Nigeria and West Africa</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>PEI Centre, Lagos</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>IELTS training, monthly</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>NGN 75,000 per month</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>https://peicentre.com/ielts-training-fees/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>British Council Nigeria / IDP</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>IELTS test fee</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>NGN 279,500 – 299,000</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>181 – 194</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>https://studyabroadly.com/updated-ielts-fees-in-nigeria-and-registration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Nigeria market aggregate</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>IELTS and English course fees, full range</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>NGN 1,000 – 2,798,000</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0.65 – 1,817</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>https://courses.laimoon.com/nigeria/languages/english/ielts/fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom and Europe</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>University of Sheffield ELTC</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Pre-sessional English</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>GBP 525 per week</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>665</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>https://sheffield.ac.uk/eltc/full-time/pre-sessional</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>University of Chester</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Pre-sessional English, 13 weeks</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>GBP 3,350</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>4241</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.chester.ac.uk/international/pre-sessional-english-language-courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>University of Chester</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Pre-sessional English, 9 weeks</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>GBP 2,600</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>3291</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.chester.ac.uk/international/pre-sessional-english-language-courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>University of Oxford Language Centre</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Pre-sessional Academic English, 6 weeks</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>GBP 3,250</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>4114</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.lang.ox.ac.uk/summer-presessional-english-course</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>University of Stirling</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Pre-sessional English, 8 weeks, ONLINE</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>GBP 5,150</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>6519</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.stir.ac.uk/international/international-students/pre-sessional-english-language-courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Executive and corporate</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>US corporate language training market</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Small group</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>15 – 35 per learner per session</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>https://edlingo.com/resources/corporate-language-training-cost/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>WHERE THE EVIDENCE DOES NOT EXIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Market or question</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>What the model does instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Qatar, Kuwait, Bahrain, Oman</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>MODELLED — INSUFFICIENT DIRECT MARKET EVIDENCE</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>No published provider tariffs found. Modelled at Saudi/UAE levels, which is an assumption about four distinct markets and is marked as one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Ghana and wider West Africa beyond Nigeria</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>MODELLED — INSUFFICIENT DIRECT MARKET EVIDENCE</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Scaled from the segments that carry direct observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>MODELLED — INSUFFICIENT DIRECT MARKET EVIDENCE</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Not a founding market in the roadmap; not researched in depth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Asia and rest of world</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>MODELLED — INSUFFICIENT DIRECT MARKET EVIDENCE</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Scaled from the segments that carry direct observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Willingness to pay for a MULTI-YEAR credentialed English pathway</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>NO DIRECT COMPARABLE FOUND</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>This is the honest centre of the problem. No provider found sells a six-level, 1,200-hour, credentialed A1–C2 pathway as one purchase. Every comparable is either a single level, a test preparation course, or a university pre-sessional. WEC-LC's product does not have a market price because the product is not on the market. The pathway prices below are therefore built UP from per-level comparables rather than read off a competitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Assumed against researched willingness to pay — the revision this plan rests on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Researched</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Elasticity</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Credibility floor</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Evidential confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Gulf executives and senior professionals</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>31000</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D35" s="13">
+        <f>C35/B35-1</f>
+        <v/>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Gulf professionals and graduate families</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>17500</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D36" s="13">
+        <f>C36/B36-1</f>
+        <v/>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom and Europe</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>19500</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>15500</v>
+      </c>
+      <c r="D37" s="13">
+        <f>C37/B37-1</f>
+        <v/>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Nigeria and West Africa</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D38" s="13">
+        <f>C38/B38-1</f>
+        <v/>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>900</v>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Asia and the rest of the world</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>9800</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D39" s="13">
+        <f>C39/B39-1</f>
+        <v/>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>modelled — insufficient direct market evidence</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorldWide English College — London Campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>22 Teaching frontier</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>The College teaches at least 60% of the people it credentials. The Directed price is the most it can charge while that holds — BOARD DECISION REQUIRED on the share, not on the price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Directed price</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Taught share</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Meets the constraint?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>0.7652050919377652</v>
+      </c>
+      <c r="C7" s="6">
+        <f>IF(B7&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>6500</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>0.7373402744912447</v>
+      </c>
+      <c r="C8" s="6">
+        <f>IF(B8&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>7000</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>0.7117117117117117</v>
+      </c>
+      <c r="C9" s="6">
+        <f>IF(B9&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>0.6870845204178537</v>
+      </c>
+      <c r="C10" s="6">
+        <f>IF(B10&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>0.6641330166270784</v>
+      </c>
+      <c r="C11" s="6">
+        <f>IF(B11&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>8500</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>0.642415596766524</v>
+      </c>
+      <c r="C12" s="6">
+        <f>IF(B12&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>9000</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>0.6214285714285714</v>
+      </c>
+      <c r="C13" s="6">
+        <f>IF(B13&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>9500</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>0.6014285714285714</v>
+      </c>
+      <c r="C14" s="5">
+        <f>IF(B14&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0.5823809523809523</v>
+      </c>
+      <c r="C15" s="6">
+        <f>IF(B15&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>10500</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>0.5642857142857143</v>
+      </c>
+      <c r="C16" s="6">
+        <f>IF(B16&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>0.5473133618640038</v>
+      </c>
+      <c r="C17" s="6">
+        <f>IF(B17&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>11500</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>0.5353390639923591</v>
+      </c>
+      <c r="C18" s="6">
+        <f>IF(B18&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>0.5237182558696694</v>
+      </c>
+      <c r="C19" s="6">
+        <f>IF(B19&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>12500</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>0.5127220355256841</v>
+      </c>
+      <c r="C20" s="6">
+        <f>IF(B20&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>13000</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>0.5024038461538461</v>
+      </c>
+      <c r="C21" s="6">
+        <f>IF(B21&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>13500</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>0.4910929224843524</v>
+      </c>
+      <c r="C22" s="6">
+        <f>IF(B22&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>14000</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>0.4800192585459798</v>
+      </c>
+      <c r="C23" s="6">
+        <f>IF(B23&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>14500</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>0.4696823869104909</v>
+      </c>
+      <c r="C24" s="6">
+        <f>IF(B24&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>0.4596153846153846</v>
+      </c>
+      <c r="C25" s="6">
+        <f>IF(B25&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>15500</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>0.449616122840691</v>
+      </c>
+      <c r="C26" s="6">
+        <f>IF(B26&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>16000</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>0.4389660124461465</v>
+      </c>
+      <c r="C27" s="6">
+        <f>IF(B27&gt;=0.6,"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Set by the Board. Change it and the price below changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Directed price</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>The highest price in the table above at which the constraint still holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>A buyer priced out of Directed does not leave — they step down to the adopted Independent route and sit the same examinations untaught. The number of people the College credentials barely moves across this range. What moves is whether it teaches them.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -27,7 +27,7 @@
     <sheet name="19 Core Plan" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="20 Price scenarios" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="21 Market evidence" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="22 Teaching frontier" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="22 Allocation framework" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="16 Summary" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1200</v>
+        <v>2100</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1750</v>
+        <v>3100</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>3100</v>
+        <v>5450</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>4950</v>
+        <v>8800</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8900</v>
+        <v>16050</v>
       </c>
     </row>
     <row r="8">
@@ -3405,19 +3405,19 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1300</v>
+        <v>2300</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1950</v>
+        <v>3500</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3500</v>
+        <v>6250</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>5650</v>
+        <v>10150</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>9900</v>
+        <v>17850</v>
       </c>
     </row>
     <row r="9">
@@ -3437,19 +3437,19 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1450</v>
+        <v>2550</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>2250</v>
+        <v>4050</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>4050</v>
+        <v>7300</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>6650</v>
+        <v>11900</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>11250</v>
+        <v>20250</v>
       </c>
     </row>
     <row r="10">
@@ -3469,19 +3469,19 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>1600</v>
+        <v>2900</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>2650</v>
+        <v>4750</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4750</v>
+        <v>8550</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>7800</v>
+        <v>14050</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>12850</v>
+        <v>23150</v>
       </c>
     </row>
     <row r="11">
@@ -3501,19 +3501,19 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>1850</v>
+        <v>3350</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3150</v>
+        <v>5700</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5750</v>
+        <v>10350</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>9500</v>
+        <v>17150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>15200</v>
+        <v>27350</v>
       </c>
     </row>
     <row r="12">
@@ -3533,19 +3533,19 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>2100</v>
+        <v>3900</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>3750</v>
+        <v>6800</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>6850</v>
+        <v>12500</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>11450</v>
+        <v>20750</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>17900</v>
+        <v>32150</v>
       </c>
     </row>
     <row r="13">
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>29059990</v>
+        <v>68180956</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>-3221563</v>
+        <v>-10139145</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>5193804</v>
+        <v>20525019</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1917</v>
+        <v>6910</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>19863</v>
+        <v>41025</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0</v>
@@ -3715,22 +3715,22 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>27268930</v>
+        <v>80452985</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4682740</v>
+        <v>8614498</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>4999314</v>
+        <v>19851569</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>974</v>
+        <v>4578</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>9835</v>
+        <v>34356</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3443477</v>
+        <v>5829352</v>
       </c>
     </row>
     <row r="9">
@@ -3740,22 +3740,22 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>37744623</v>
+        <v>95508176</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>2274765</v>
+        <v>37432254</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>6667802</v>
+        <v>17395110</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>2648</v>
+        <v>3851</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>27760</v>
+        <v>39164</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>2225710</v>
+        <v>22593946</v>
       </c>
     </row>
   </sheetData>
@@ -3895,35 +3895,35 @@
         <v>2027</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>142300</v>
+        <v>362586</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>3131</v>
+        <v>7977</v>
       </c>
       <c r="H7" s="10">
         <f>F7-G7</f>
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>61004</v>
+        <v>127139</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>58568</v>
+        <v>65714</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>363820</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>7654</v>
+        <v>19504</v>
       </c>
       <c r="M7" s="15">
         <f>H7-I7-J7-K7-L7</f>
@@ -3946,35 +3946,35 @@
         <v>2028</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>240</v>
+        <v>327</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>258</v>
+        <v>354</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>574259</v>
+        <v>1395861</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>12634</v>
+        <v>30709</v>
       </c>
       <c r="H8" s="10">
         <f>F8-G8</f>
         <v/>
       </c>
       <c r="I8" s="10" t="n">
-        <v>246074</v>
+        <v>488773</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>205434</v>
+        <v>215892</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>30889</v>
+        <v>75083</v>
       </c>
       <c r="M8" s="15">
         <f>H8-I8-J8-K8-L8</f>
@@ -3997,35 +3997,35 @@
         <v>2029</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>438</v>
+        <v>608</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>501</v>
+        <v>694</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1173613</v>
+        <v>2888367</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>25819</v>
+        <v>63544</v>
       </c>
       <c r="H9" s="10">
         <f>F9-G9</f>
         <v/>
       </c>
       <c r="I9" s="10" t="n">
-        <v>502740</v>
+        <v>1010561</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>374579</v>
+        <v>401627</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>63129</v>
+        <v>155365</v>
       </c>
       <c r="M9" s="15">
         <f>H9-I9-J9-K9-L9</f>
@@ -4048,35 +4048,35 @@
         <v>2030</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>895</v>
+        <v>991</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1009</v>
+        <v>1150</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2342068</v>
+        <v>4861491</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>51525</v>
+        <v>106953</v>
       </c>
       <c r="H10" s="10">
         <f>F10-G10</f>
         <v/>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1003337</v>
+        <v>1700507</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>766194</v>
+        <v>654400</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>125980</v>
+        <v>261500</v>
       </c>
       <c r="M10" s="15">
         <f>H10-I10-J10-K10-L10</f>
@@ -4099,35 +4099,35 @@
         <v>2031</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1217</v>
+        <v>1519</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1451</v>
+        <v>1778</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3512020</v>
+        <v>7571839</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>77264</v>
+        <v>166580</v>
       </c>
       <c r="H11" s="10">
         <f>F11-G11</f>
         <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1504156</v>
+        <v>2648264</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1040969</v>
+        <v>1002947</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>188912</v>
+        <v>407289</v>
       </c>
       <c r="M11" s="15">
         <f>H11-I11-J11-K11-L11</f>
@@ -4150,35 +4150,35 @@
         <v>2032</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1560</v>
+        <v>2298</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1878</v>
+        <v>2695</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>4578989</v>
+        <v>11492168</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>100738</v>
+        <v>252828</v>
       </c>
       <c r="H12" s="10">
         <f>F12-G12</f>
         <v/>
       </c>
       <c r="I12" s="10" t="n">
-        <v>1961047</v>
+        <v>4019306</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1335045</v>
+        <v>1516732</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>246304</v>
+        <v>618164</v>
       </c>
       <c r="M12" s="15">
         <f>H12-I12-J12-K12-L12</f>
@@ -4201,35 +4201,35 @@
         <v>2033</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>1892</v>
+        <v>2862</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>2300</v>
+        <v>3463</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5645475</v>
+        <v>15144567</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>124200</v>
+        <v>333180</v>
       </c>
       <c r="H13" s="10">
         <f>F13-G13</f>
         <v/>
       </c>
       <c r="I13" s="10" t="n">
-        <v>2417694</v>
+        <v>5294691</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1618733</v>
+        <v>1888697</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>303670</v>
+        <v>814626</v>
       </c>
       <c r="M13" s="15">
         <f>H13-I13-J13-K13-L13</f>
@@ -4252,35 +4252,35 @@
         <v>2034</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2099</v>
+        <v>3053</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2594</v>
+        <v>3801</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>6440295</v>
+        <v>17001077</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>141686</v>
+        <v>374024</v>
       </c>
       <c r="H14" s="10">
         <f>F14-G14</f>
         <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>2757896</v>
+        <v>5941820</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1796092</v>
+        <v>2015225</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>346423</v>
+        <v>914488</v>
       </c>
       <c r="M14" s="15">
         <f>H14-I14-J14-K14-L14</f>
@@ -4303,35 +4303,35 @@
         <v>2035</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2099</v>
+        <v>3053</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>2648</v>
+        <v>3851</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>6667802</v>
+        <v>17395110</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>146692</v>
+        <v>382692</v>
       </c>
       <c r="H15" s="10">
         <f>F15-G15</f>
         <v/>
       </c>
       <c r="I15" s="10" t="n">
-        <v>2855093</v>
+        <v>6078677</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>1796092</v>
+        <v>2015225</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>358661</v>
+        <v>935683</v>
       </c>
       <c r="M15" s="15">
         <f>H15-I15-J15-K15-L15</f>
@@ -4354,35 +4354,35 @@
         <v>2036</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2099</v>
+        <v>3053</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2648</v>
+        <v>3851</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>6667802</v>
+        <v>17395110</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>146692</v>
+        <v>382692</v>
       </c>
       <c r="H16" s="10">
         <f>F16-G16</f>
         <v/>
       </c>
       <c r="I16" s="10" t="n">
-        <v>2855093</v>
+        <v>6078677</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1796092</v>
+        <v>2015225</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>358661</v>
+        <v>935683</v>
       </c>
       <c r="M16" s="15">
         <f>H16-I16-J16-K16-L16</f>
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>22581373</v>
+        <v>58985611</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>-4423959</v>
+        <v>16920257</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3970149</v>
+        <v>10280653</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1553</v>
+        <v>2259</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1830</v>
+        <v>2661</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>17269</v>
+        <v>25343</v>
       </c>
     </row>
     <row r="8">
@@ -4549,22 +4549,22 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>37744623</v>
+        <v>95508176</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2274765</v>
+        <v>37432254</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>6667802</v>
+        <v>17395110</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>2099</v>
+        <v>3053</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>2648</v>
+        <v>3851</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>27760</v>
+        <v>39164</v>
       </c>
     </row>
     <row r="9">
@@ -4574,22 +4574,22 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>57305109</v>
+        <v>124374155</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>10792427</v>
+        <v>54132195</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>10143762</v>
+        <v>23121960</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>2687</v>
+        <v>3594</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>3597</v>
+        <v>4811</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>40901</v>
+        <v>51003</v>
       </c>
     </row>
   </sheetData>
@@ -5977,12 +5977,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5995,321 +6001,983 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22 Teaching frontier</t>
+          <t>22 Allocation framework</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>The College teaches at least 60% of the people it credentials. The Directed price is the most it can charge while that holds — BOARD DECISION REQUIRED on the share, not on the price.</t>
+          <t>BOARD DECISION REQUIRED. Every figure below is a proposed governance target, not a historical result. The tariff is solved backwards from it.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Directed price</t>
+          <t>Allocation</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Taught share</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Meets the constraint?</t>
+          <t>At the proposed tariff</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Definition</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
-        <v>6000</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.7652050919377652</v>
-      </c>
-      <c r="C7" s="6">
-        <f>IF(B7&gt;=0.6,"yes","no")</f>
-        <v/>
+        <v>0.25</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0.3595990133326435</v>
+      </c>
+      <c r="D7" s="9">
+        <f>C7-B7</f>
+        <v/>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>All employed people: academic delivery, examinations, registry, admissions, student support, platform engineering, academic standards, finance and compliance, and institutional leadership, inclusive of on-costs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
-        <v>6500</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>LMS and Technology</t>
+        </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0.7373402744912447</v>
-      </c>
-      <c r="C8" s="6">
-        <f>IF(B8&gt;=0.6,"yes","no")</f>
-        <v/>
+        <v>0.05</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0.0106360054989733</v>
+      </c>
+      <c r="D8" s="9">
+        <f>C8-B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>The learning platform, hosting, authentication, storage, media, security and the tooling the College runs on. Salaries of the people who build it sit in Payroll.</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
-        <v>7000</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.7117117117117117</v>
-      </c>
-      <c r="C9" s="6">
-        <f>IF(B9&gt;=0.6,"yes","no")</f>
-        <v/>
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>0.01301511918592931</v>
+      </c>
+      <c r="D9" s="9">
+        <f>C9-B9</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Legal, accounting, insurance, audit, professional services, the London registered office, examinations administration, and institutional administration.</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>7500</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Marketing and Student Acquisition</t>
+        </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.6870845204178537</v>
-      </c>
-      <c r="C10" s="6">
-        <f>IF(B10&gt;=0.6,"yes","no")</f>
-        <v/>
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0.1158500866047987</v>
+      </c>
+      <c r="D10" s="9">
+        <f>C10-B10</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Media, content, campaigns, partnership development and the admissions conversation — the cost of being found and understood. Salaries of the people who do it sit in Payroll.</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>8000</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Institutional Reserve</t>
+        </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.6641330166270784</v>
-      </c>
-      <c r="C11" s="6">
-        <f>IF(B11&gt;=0.6,"yes","no")</f>
-        <v/>
+        <v>0.25</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0.2504498876888276</v>
+      </c>
+      <c r="D11" s="9">
+        <f>C11-B11</f>
+        <v/>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Restricted or designated institutional capital retained to strengthen liquidity, fund major institutional initiatives, absorb exceptional shocks, support future expansion, and maintain long-term financial resilience.</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>8500</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Strategic and Founders' Allocation</t>
+        </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.642415596766524</v>
-      </c>
-      <c r="C12" s="6">
-        <f>IF(B12&gt;=0.6,"yes","no")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>9000</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>0.6214285714285714</v>
-      </c>
-      <c r="C13" s="6">
-        <f>IF(B13&gt;=0.6,"yes","no")</f>
-        <v/>
+        <v>0.25</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>0.2504498876888276</v>
+      </c>
+      <c r="D12" s="9">
+        <f>C12-B12</f>
+        <v/>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>A discretionary institutional allocation available for founder remuneration, strategic investment, expansion, intellectual property development, new campuses and markets, acquisitions, exceptional executive compensation, and other Board-authorised strategic purposes.</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
-        <v>9500</v>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>0.6014285714285714</v>
-      </c>
-      <c r="C14" s="5">
-        <f>IF(B14&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Gross collected revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>17395110</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>0.5823809523809523</v>
-      </c>
-      <c r="C15" s="6">
-        <f>IF(B15&gt;=0.6,"yes","no")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
-        <v>10500</v>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="C16" s="6">
-        <f>IF(B16&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Retained (reserve + strategic)</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>8713207</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>0.5008997753776553</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>11000</v>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>0.5473133618640038</v>
-      </c>
-      <c r="C17" s="6">
-        <f>IF(B17&gt;=0.6,"yes","no")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>11500</v>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>0.5353390639923591</v>
-      </c>
-      <c r="C18" s="6">
-        <f>IF(B18&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>The two retained lines are designated institutional capital. The Strategic and Founders' Allocation is NOT automatically withdrawable founder income, and no distribution from it is modelled anywhere in this workbook.</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>0.5237182558696694</v>
-      </c>
-      <c r="C19" s="6">
-        <f>IF(B19&gt;=0.6,"yes","no")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>12500</v>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>0.5127220355256841</v>
-      </c>
-      <c r="C20" s="6">
-        <f>IF(B20&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>THE SWEEP THE PRICE IS SOLVED FROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Tariff multiple</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Tutored</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Executive Core</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Learners</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Retained</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>13000</v>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>0.5024038461538461</v>
-      </c>
-      <c r="C21" s="6">
-        <f>IF(B21&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A21" s="14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>10250</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>16750</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>30250</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>20474383</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>4544</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>0.5549478156433476</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>0.1222572128302963</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0.2983779721587921</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>13500</v>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>0.4910929224843524</v>
-      </c>
-      <c r="C22" s="6">
-        <f>IF(B22&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A22" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>11950</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>19550</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>35300</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>19522653</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>3960</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>0.4815352907200529</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>0.1192553081796823</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>0.3753820664131277</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>14000</v>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>0.4800192585459798</v>
-      </c>
-      <c r="C23" s="6">
-        <f>IF(B23&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A23" s="14" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>13700</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>22300</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>40300</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>18728430</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>3550</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>0.4294276461165445</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>0.1168922862194001</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>0.430139528429292</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>14500</v>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>0.4696823869104909</v>
-      </c>
-      <c r="C24" s="6">
-        <f>IF(B24&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A24" s="14" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>15400</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>25100</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>45350</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>18026952</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>3260</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>0.3897782252626893</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>0.1158619049964742</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>0.4708556110295951</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>15000</v>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>0.4596153846153846</v>
-      </c>
-      <c r="C25" s="6">
-        <f>IF(B25&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A25" s="22" t="n">
+        <v>0.9999999999999999</v>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>17100</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>27900</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>50400</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>17395110</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>3053</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.3595990133326435</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>0.1158500866047987</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>0.5008997753776553</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
-        <v>15500</v>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>0.449616122840691</v>
-      </c>
-      <c r="C26" s="6">
-        <f>IF(B26&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A26" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>18800</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>30700</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>55450</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>16841536</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>2904</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>0.3360145026805764</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>0.1164818339609879</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>0.5236042039905265</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
-        <v>16000</v>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>0.4389660124461465</v>
-      </c>
-      <c r="C27" s="6">
-        <f>IF(B27&gt;=0.6,"yes","no")</f>
-        <v/>
+      <c r="A27" s="14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>20500</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>33500</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>60500</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>16356111</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>2795</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>0.3173124945999873</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>0.1175803343472051</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>0.5408979089702293</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>22250</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>36250</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>65500</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>15930220</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>2718</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>0.3032307927276961</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>0.1190714252533863</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>0.5531209574204794</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Set by the Board. Change it and the price below changes.</t>
-        </is>
+      <c r="A29" s="14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>23950</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>39050</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>70550</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>15545294</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>2661</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>0.2907002022883821</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>0.1208509147527219</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>0.5634889496989965</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Directed price</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n">
-        <v>9500</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>The highest price in the table above at which the constraint still holds.</t>
-        </is>
+      <c r="A30" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>25650</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>41850</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>75600</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>15188128</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>2620</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>0.281012818779319</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>0.1229767091770625</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>0.5706161100725128</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>27350</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>44650</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>80650</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>14840247</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>2560</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>0.2725675734647127</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>0.124124551296215</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>0.5775583916881233</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>A buyer priced out of Directed does not leave — they step down to the adopted Independent route and sit the same examinations untaught. The number of people the College credentials barely moves across this range. What moves is whether it teaches them.</t>
-        </is>
+      <c r="A32" s="14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>47450</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>85700</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>14514522</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>2502</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>0.2644025437282586</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>0.1251534153174317</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>0.5843540756025433</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>50200</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>90700</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>14213299</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>2455</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>0.2582893333190636</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>0.1263313323669614</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>0.5889328718224852</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>1.900000000000001</v>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>32500</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>53000</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>95750</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>13931012</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>2415</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>0.2529421094553104</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>0.1276399015376629</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>0.592610461018543</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>34200</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>55800</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>100800</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>13666639</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>2381</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>0.2476667265495177</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>0.1290602612683338</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>0.5960990360699771</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>2.100000000000001</v>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>35900</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>58600</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>105850</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>13418011</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>2352</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>0.2440138740927893</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>0.1305800092129899</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>0.5978525796001546</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>37600</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>61400</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>110900</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>13183374</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>2328</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>0.2407757297742488</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>0.132188315373591</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>0.5991001613150656</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>39350</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>64150</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>115900</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>12961540</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>2308</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>0.2378970404864541</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>0.1338902630397314</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>0.5998904467390367</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="n">
+        <v>2.400000000000001</v>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>41050</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>66950</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>120950</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>12750526</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>0.2356321459870337</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>0.1356503253277551</v>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>0.6000104200055989</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="n">
+        <v>2.500000000000001</v>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>42750</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>69750</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>12549708</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>0.2343153167408257</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>0.137473796203067</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0.599101212887686</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>44450</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>72550</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>131050</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>12358078</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>2264</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>0.232330409064089</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>0.139355650611689</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>0.5988201726171776</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="n">
+        <v>2.700000000000001</v>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>46150</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>75350</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>136100</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>12174805</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>2254</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>0.2306246389309383</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>0.1412910514788533</v>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>0.598200228564673</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="n">
+        <v>2.800000000000001</v>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>47900</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>78100</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>141100</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>11999000</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>2246</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>0.2300156995723689</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>0.1432993582798567</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>0.596397664490099</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="n">
+        <v>2.900000000000001</v>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>49600</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>80900</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>146150</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>11830304</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>2239</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>0.2298273530660217</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>0.1453307539687907</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>0.5941528563853372</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="n">
+        <v>3.000000000000001</v>
+      </c>
+      <c r="B45" s="10" t="n">
+        <v>51300</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>83700</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>151200</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>11668095</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>2234</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>0.2291900699682136</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>0.1474036678652342</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>0.5923211347486614</v>
       </c>
     </row>
   </sheetData>

--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -3740,22 +3740,22 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>95508176</v>
+        <v>73062467</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>37432254</v>
+        <v>20236078</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>17395110</v>
+        <v>13217412</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>3851</v>
+        <v>3408</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>39164</v>
+        <v>34887</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>22593946</v>
+        <v>12453581</v>
       </c>
     </row>
   </sheetData>
@@ -3895,35 +3895,35 @@
         <v>2027</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>362586</v>
+        <v>275725</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>7977</v>
+        <v>6066</v>
       </c>
       <c r="H7" s="10">
         <f>F7-G7</f>
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>127139</v>
+        <v>119179</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>65714</v>
+        <v>55673</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>363820</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>19504</v>
+        <v>14831</v>
       </c>
       <c r="M7" s="15">
         <f>H7-I7-J7-K7-L7</f>
@@ -3946,35 +3946,35 @@
         <v>2028</v>
       </c>
       <c r="C8" s="8" t="n">
+        <v>304</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>327</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>354</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1395861</v>
+        <v>1105833</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>30709</v>
+        <v>24328</v>
       </c>
       <c r="H8" s="10">
         <f>F8-G8</f>
         <v/>
       </c>
       <c r="I8" s="10" t="n">
-        <v>488773</v>
+        <v>477974</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>215892</v>
+        <v>191932</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>75083</v>
+        <v>59483</v>
       </c>
       <c r="M8" s="15">
         <f>H8-I8-J8-K8-L8</f>
@@ -3997,35 +3997,35 @@
         <v>2029</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>608</v>
+        <v>562</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>12</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>2888367</v>
+        <v>2293688</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>63544</v>
+        <v>50461</v>
       </c>
       <c r="H9" s="10">
         <f>F9-G9</f>
         <v/>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1010561</v>
+        <v>991388</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>401627</v>
+        <v>355043</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>155365</v>
+        <v>123377</v>
       </c>
       <c r="M9" s="15">
         <f>H9-I9-J9-K9-L9</f>
@@ -4048,35 +4048,35 @@
         <v>2030</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>991</v>
+        <v>917</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1150</v>
+        <v>1063</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>20</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4861491</v>
+        <v>3858680</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>106953</v>
+        <v>84891</v>
       </c>
       <c r="H10" s="10">
         <f>F10-G10</f>
         <v/>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1700507</v>
+        <v>1667813</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>654400</v>
+        <v>579182</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>261500</v>
+        <v>207558</v>
       </c>
       <c r="M10" s="15">
         <f>H10-I10-J10-K10-L10</f>
@@ -4099,35 +4099,35 @@
         <v>2031</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1519</v>
+        <v>1404</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1778</v>
+        <v>1644</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>31</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>7571839</v>
+        <v>6010230</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>166580</v>
+        <v>132225</v>
       </c>
       <c r="H11" s="10">
         <f>F11-G11</f>
         <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>2648264</v>
+        <v>2597758</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1002947</v>
+        <v>887387</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>407289</v>
+        <v>323290</v>
       </c>
       <c r="M11" s="15">
         <f>H11-I11-J11-K11-L11</f>
@@ -4150,35 +4150,35 @@
         <v>2032</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2298</v>
+        <v>2033</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2695</v>
+        <v>2400</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>11492168</v>
+        <v>8836639</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>252828</v>
+        <v>194406</v>
       </c>
       <c r="H12" s="10">
         <f>F12-G12</f>
         <v/>
       </c>
       <c r="I12" s="10" t="n">
-        <v>4019306</v>
+        <v>3819390</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1516732</v>
+        <v>1284515</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>618164</v>
+        <v>475323</v>
       </c>
       <c r="M12" s="15">
         <f>H12-I12-J12-K12-L12</f>
@@ -4201,35 +4201,35 @@
         <v>2033</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2862</v>
+        <v>2495</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>3463</v>
+        <v>3026</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>15144567</v>
+        <v>11392861</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>333180</v>
+        <v>250643</v>
       </c>
       <c r="H13" s="10">
         <f>F13-G13</f>
         <v/>
       </c>
       <c r="I13" s="10" t="n">
-        <v>5294691</v>
+        <v>4924223</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1888697</v>
+        <v>1577009</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>814626</v>
+        <v>612822</v>
       </c>
       <c r="M13" s="15">
         <f>H13-I13-J13-K13-L13</f>
@@ -4252,35 +4252,35 @@
         <v>2034</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>3053</v>
+        <v>2702</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3801</v>
+        <v>3354</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>17001077</v>
+        <v>12853987</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>374024</v>
+        <v>282788</v>
       </c>
       <c r="H14" s="10">
         <f>F14-G14</f>
         <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>5941820</v>
+        <v>5555730</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>2015225</v>
+        <v>1707312</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>914488</v>
+        <v>691416</v>
       </c>
       <c r="M14" s="15">
         <f>H14-I14-J14-K14-L14</f>
@@ -4303,35 +4303,35 @@
         <v>2035</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>3053</v>
+        <v>2702</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>3851</v>
+        <v>3408</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>17395110</v>
+        <v>13217412</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>382692</v>
+        <v>290783</v>
       </c>
       <c r="H15" s="10">
         <f>F15-G15</f>
         <v/>
       </c>
       <c r="I15" s="10" t="n">
-        <v>6078677</v>
+        <v>5712795</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>2015225</v>
+        <v>1707312</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>935683</v>
+        <v>710965</v>
       </c>
       <c r="M15" s="15">
         <f>H15-I15-J15-K15-L15</f>
@@ -4354,35 +4354,35 @@
         <v>2036</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3053</v>
+        <v>2702</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3851</v>
+        <v>3408</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>17395110</v>
+        <v>13217412</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>382692</v>
+        <v>290783</v>
       </c>
       <c r="H16" s="10">
         <f>F16-G16</f>
         <v/>
       </c>
       <c r="I16" s="10" t="n">
-        <v>6078677</v>
+        <v>5712795</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>2015225</v>
+        <v>1707312</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>935683</v>
+        <v>710965</v>
       </c>
       <c r="M16" s="15">
         <f>H16-I16-J16-K16-L16</f>
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>58985611</v>
+        <v>44544346</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>16920257</v>
+        <v>6746570</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>10280653</v>
+        <v>7813545</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2259</v>
+        <v>1999</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>2661</v>
+        <v>2355</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>25343</v>
+        <v>22278</v>
       </c>
     </row>
     <row r="8">
@@ -4549,22 +4549,22 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>95508176</v>
+        <v>73062467</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>37432254</v>
+        <v>20236078</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>17395110</v>
+        <v>13217412</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>3053</v>
+        <v>2702</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>3851</v>
+        <v>3408</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>39164</v>
+        <v>34887</v>
       </c>
     </row>
     <row r="9">
@@ -4574,22 +4574,22 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>124374155</v>
+        <v>97134390</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>54132195</v>
+        <v>32646405</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>23121960</v>
+        <v>17971973</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>3594</v>
+        <v>3162</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>4811</v>
+        <v>4232</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>51003</v>
+        <v>45551</v>
       </c>
     </row>
   </sheetData>

--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>68180956</v>
+        <v>63892513</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>-10139145</v>
+        <v>-11411077</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>20525019</v>
+        <v>16122358</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>6910</v>
+        <v>5331</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>41025</v>
+        <v>39043</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0</v>
@@ -3715,22 +3715,22 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>80452985</v>
+        <v>76416524</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>8614498</v>
+        <v>7686491</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>19851569</v>
+        <v>16687817</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4578</v>
+        <v>3812</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>34356</v>
+        <v>32326</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>5829352</v>
+        <v>5279684</v>
       </c>
     </row>
     <row r="9">
@@ -3740,22 +3740,22 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>73062467</v>
+        <v>74926660</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>20236078</v>
+        <v>18681568</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>13217412</v>
+        <v>13965880</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>3408</v>
+        <v>3756</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>34887</v>
+        <v>37320</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>12453581</v>
+        <v>11550804</v>
       </c>
     </row>
   </sheetData>
@@ -3895,35 +3895,35 @@
         <v>2027</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>275725</v>
+        <v>291382</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>6066</v>
+        <v>6410</v>
       </c>
       <c r="H7" s="10">
         <f>F7-G7</f>
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>119179</v>
+        <v>132314</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>55673</v>
+        <v>61935</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>363820</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>14831</v>
+        <v>15673</v>
       </c>
       <c r="M7" s="15">
         <f>H7-I7-J7-K7-L7</f>
@@ -3946,35 +3946,35 @@
         <v>2028</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1105833</v>
+        <v>1057502</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>24328</v>
+        <v>23265</v>
       </c>
       <c r="H8" s="10">
         <f>F8-G8</f>
         <v/>
       </c>
       <c r="I8" s="10" t="n">
-        <v>477974</v>
+        <v>480282</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>191932</v>
+        <v>189913</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>59483</v>
+        <v>56883</v>
       </c>
       <c r="M8" s="15">
         <f>H8-I8-J8-K8-L8</f>
@@ -3997,35 +3997,35 @@
         <v>2029</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>12</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>2293688</v>
+        <v>2178580</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>50461</v>
+        <v>47929</v>
       </c>
       <c r="H9" s="10">
         <f>F9-G9</f>
         <v/>
       </c>
       <c r="I9" s="10" t="n">
-        <v>991388</v>
+        <v>989519</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>355043</v>
+        <v>356163</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>123377</v>
+        <v>117186</v>
       </c>
       <c r="M9" s="15">
         <f>H9-I9-J9-K9-L9</f>
@@ -4048,35 +4048,35 @@
         <v>2030</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1063</v>
+        <v>1054</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>20</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3858680</v>
+        <v>3669268</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>84891</v>
+        <v>80724</v>
       </c>
       <c r="H10" s="10">
         <f>F10-G10</f>
         <v/>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1667813</v>
+        <v>1666643</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>579182</v>
+        <v>579430</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>207558</v>
+        <v>197370</v>
       </c>
       <c r="M10" s="15">
         <f>H10-I10-J10-K10-L10</f>
@@ -4099,35 +4099,35 @@
         <v>2031</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1404</v>
+        <v>1392</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1644</v>
+        <v>1630</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>31</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>6010230</v>
+        <v>5713889</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>132225</v>
+        <v>125706</v>
       </c>
       <c r="H11" s="10">
         <f>F11-G11</f>
         <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>2597758</v>
+        <v>2595375</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>887387</v>
+        <v>888343</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>323290</v>
+        <v>307350</v>
       </c>
       <c r="M11" s="15">
         <f>H11-I11-J11-K11-L11</f>
@@ -4150,35 +4150,35 @@
         <v>2032</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2033</v>
+        <v>2106</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2400</v>
+        <v>2470</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>8836639</v>
+        <v>8672468</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>194406</v>
+        <v>190794</v>
       </c>
       <c r="H12" s="10">
         <f>F12-G12</f>
         <v/>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3819390</v>
+        <v>3939240</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1284515</v>
+        <v>1343311</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>475323</v>
+        <v>466492</v>
       </c>
       <c r="M12" s="15">
         <f>H12-I12-J12-K12-L12</f>
@@ -4201,35 +4201,35 @@
         <v>2033</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2495</v>
+        <v>2754</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>3026</v>
+        <v>3304</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>11392861</v>
+        <v>11823170</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>250643</v>
+        <v>260110</v>
       </c>
       <c r="H13" s="10">
         <f>F13-G13</f>
         <v/>
       </c>
       <c r="I13" s="10" t="n">
-        <v>4924223</v>
+        <v>5370533</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1577009</v>
+        <v>1756897</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>612822</v>
+        <v>635968</v>
       </c>
       <c r="M13" s="15">
         <f>H13-I13-J13-K13-L13</f>
@@ -4252,35 +4252,35 @@
         <v>2034</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2702</v>
+        <v>2978</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3354</v>
+        <v>3698</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>12853987</v>
+        <v>13588641</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>282788</v>
+        <v>298950</v>
       </c>
       <c r="H14" s="10">
         <f>F14-G14</f>
         <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>5555730</v>
+        <v>6172752</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1707312</v>
+        <v>1899339</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>691416</v>
+        <v>730933</v>
       </c>
       <c r="M14" s="15">
         <f>H14-I14-J14-K14-L14</f>
@@ -4303,35 +4303,35 @@
         <v>2035</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2702</v>
+        <v>2978</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>3408</v>
+        <v>3756</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>13217412</v>
+        <v>13965880</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>290783</v>
+        <v>307249</v>
       </c>
       <c r="H15" s="10">
         <f>F15-G15</f>
         <v/>
       </c>
       <c r="I15" s="10" t="n">
-        <v>5712795</v>
+        <v>6344237</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>1707312</v>
+        <v>1899339</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>710965</v>
+        <v>751225</v>
       </c>
       <c r="M15" s="15">
         <f>H15-I15-J15-K15-L15</f>
@@ -4354,35 +4354,35 @@
         <v>2036</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2702</v>
+        <v>2978</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3408</v>
+        <v>3756</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>13217412</v>
+        <v>13965880</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>290783</v>
+        <v>307249</v>
       </c>
       <c r="H16" s="10">
         <f>F16-G16</f>
         <v/>
       </c>
       <c r="I16" s="10" t="n">
-        <v>5712795</v>
+        <v>6344237</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1707312</v>
+        <v>1899339</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>710965</v>
+        <v>751225</v>
       </c>
       <c r="M16" s="15">
         <f>H16-I16-J16-K16-L16</f>
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>44544346</v>
+        <v>47061856</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>6746570</v>
+        <v>5883180</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>7813545</v>
+        <v>8256398</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1999</v>
+        <v>2203</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>2355</v>
+        <v>2595</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>22278</v>
+        <v>24551</v>
       </c>
     </row>
     <row r="8">
@@ -4549,22 +4549,22 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>73062467</v>
+        <v>74926660</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>20236078</v>
+        <v>18681568</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>13217412</v>
+        <v>13965880</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>2702</v>
+        <v>2978</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>3408</v>
+        <v>3756</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>34887</v>
+        <v>37320</v>
       </c>
     </row>
     <row r="9">
@@ -4574,22 +4574,22 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>97134390</v>
+        <v>98853195</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>32646405</v>
+        <v>30704948</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>17971973</v>
+        <v>18952542</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>3162</v>
+        <v>3476</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>4232</v>
+        <v>4653</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>45551</v>
+        <v>48363</v>
       </c>
     </row>
   </sheetData>
@@ -6269,19 +6269,19 @@
         <v>30250</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>20474383</v>
+        <v>18039853</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>4544</v>
+        <v>4000</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.5549478156433476</v>
+        <v>0.5495767520971756</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.1222572128302963</v>
+        <v>0.1387561750087432</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0.2983779721587921</v>
+        <v>0.2857462257675683</v>
       </c>
     </row>
     <row r="22">
@@ -6298,19 +6298,19 @@
         <v>35300</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>19522653</v>
+        <v>18114228</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3960</v>
+        <v>3690</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.4815352907200529</v>
+        <v>0.4794499741592875</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.1192553081796823</v>
+        <v>0.1285276965708944</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>0.3753820664131277</v>
+        <v>0.3672244946210855</v>
       </c>
     </row>
     <row r="23">
@@ -6327,19 +6327,19 @@
         <v>40300</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>18728430</v>
+        <v>18172602</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>3550</v>
+        <v>3457</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.4294276461165445</v>
+        <v>0.4289409633204131</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.1168922862194001</v>
+        <v>0.1204675588008806</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0.430139528429292</v>
+        <v>0.4266349223507077</v>
       </c>
     </row>
     <row r="24">

--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>5450</v>
+        <v>5700</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>8800</v>
+        <v>9150</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>16050</v>
+        <v>16700</v>
       </c>
     </row>
     <row r="8">
@@ -3405,19 +3405,19 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3500</v>
+        <v>3650</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>6250</v>
+        <v>6500</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>10150</v>
+        <v>10550</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>17850</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="9">
@@ -3437,19 +3437,19 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>2550</v>
+        <v>2700</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>4050</v>
+        <v>4200</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>7300</v>
+        <v>7600</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>11900</v>
+        <v>12400</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>20250</v>
+        <v>21050</v>
       </c>
     </row>
     <row r="10">
@@ -3469,19 +3469,19 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>4750</v>
+        <v>4900</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>8550</v>
+        <v>8900</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>14050</v>
+        <v>14600</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>23150</v>
+        <v>24050</v>
       </c>
     </row>
     <row r="11">
@@ -3501,19 +3501,19 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3350</v>
+        <v>3500</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5700</v>
+        <v>5900</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>10350</v>
+        <v>10800</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>17150</v>
+        <v>17850</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>27350</v>
+        <v>28450</v>
       </c>
     </row>
     <row r="12">
@@ -3533,19 +3533,19 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>6800</v>
+        <v>7150</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>12500</v>
+        <v>12900</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>20750</v>
+        <v>21550</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>32150</v>
+        <v>33450</v>
       </c>
     </row>
     <row r="13">
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>63892513</v>
+        <v>52571072</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>-11411077</v>
+        <v>-10611226</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>16122358</v>
+        <v>15450829</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>5331</v>
+        <v>5206</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>39043</v>
+        <v>32147</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>76416524</v>
+        <v>63983540</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7686491</v>
+        <v>5371978</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>16687817</v>
@@ -3727,10 +3727,10 @@
         <v>3812</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>32326</v>
+        <v>27038</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>5279684</v>
+        <v>4140126</v>
       </c>
     </row>
     <row r="9">
@@ -3740,22 +3740,22 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>74926660</v>
+        <v>72868799</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>18681568</v>
+        <v>19765357</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>13965880</v>
+        <v>14550296</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>3756</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>37320</v>
+        <v>34858</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>11550804</v>
+        <v>12238554</v>
       </c>
     </row>
   </sheetData>
@@ -3895,35 +3895,35 @@
         <v>2027</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>291382</v>
+        <v>144281</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>6410</v>
+        <v>3174</v>
       </c>
       <c r="H7" s="10">
         <f>F7-G7</f>
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>132314</v>
+        <v>50590</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>61935</v>
+        <v>45435</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>363820</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>15673</v>
+        <v>7761</v>
       </c>
       <c r="M7" s="15">
         <f>H7-I7-J7-K7-L7</f>
@@ -3946,35 +3946,35 @@
         <v>2028</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>323</v>
+        <v>256</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1057502</v>
+        <v>846035</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>23265</v>
+        <v>18613</v>
       </c>
       <c r="H8" s="10">
         <f>F8-G8</f>
         <v/>
       </c>
       <c r="I8" s="10" t="n">
-        <v>480282</v>
+        <v>319041</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>189913</v>
+        <v>180448</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>56883</v>
+        <v>45508</v>
       </c>
       <c r="M8" s="15">
         <f>H8-I8-J8-K8-L8</f>
@@ -3997,35 +3997,35 @@
         <v>2029</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>559</v>
+        <v>430</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>2178580</v>
+        <v>1770193</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>47929</v>
+        <v>38944</v>
       </c>
       <c r="H9" s="10">
         <f>F9-G9</f>
         <v/>
       </c>
       <c r="I9" s="10" t="n">
-        <v>989519</v>
+        <v>746999</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>356163</v>
+        <v>274002</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>117186</v>
+        <v>95219</v>
       </c>
       <c r="M9" s="15">
         <f>H9-I9-J9-K9-L9</f>
@@ -4048,35 +4048,35 @@
         <v>2030</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>908</v>
+        <v>733</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1054</v>
+        <v>845</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3669268</v>
+        <v>3046745</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>80724</v>
+        <v>67028</v>
       </c>
       <c r="H10" s="10">
         <f>F10-G10</f>
         <v/>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1666643</v>
+        <v>1328516</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>579430</v>
+        <v>467457</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>197370</v>
+        <v>163884</v>
       </c>
       <c r="M10" s="15">
         <f>H10-I10-J10-K10-L10</f>
@@ -4099,35 +4099,35 @@
         <v>2031</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1392</v>
+        <v>1178</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1630</v>
+        <v>1370</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5713889</v>
+        <v>4973433</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>125706</v>
+        <v>109416</v>
       </c>
       <c r="H11" s="10">
         <f>F11-G11</f>
         <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>2595375</v>
+        <v>2168626</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>888343</v>
+        <v>751686</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>307350</v>
+        <v>267521</v>
       </c>
       <c r="M11" s="15">
         <f>H11-I11-J11-K11-L11</f>
@@ -4150,35 +4150,35 @@
         <v>2032</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2106</v>
+        <v>1795</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2470</v>
+        <v>2103</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>8672468</v>
+        <v>7684272</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>190794</v>
+        <v>169054</v>
       </c>
       <c r="H12" s="10">
         <f>F12-G12</f>
         <v/>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3939240</v>
+        <v>3350650</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1343311</v>
+        <v>1144808</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>466492</v>
+        <v>413337</v>
       </c>
       <c r="M12" s="15">
         <f>H12-I12-J12-K12-L12</f>
@@ -4201,35 +4201,35 @@
         <v>2033</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2754</v>
+        <v>2627</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>3304</v>
+        <v>3096</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>11823170</v>
+        <v>11370680</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>260110</v>
+        <v>250155</v>
       </c>
       <c r="H13" s="10">
         <f>F13-G13</f>
         <v/>
       </c>
       <c r="I13" s="10" t="n">
-        <v>5370533</v>
+        <v>4958052</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1756897</v>
+        <v>1675680</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>635968</v>
+        <v>611629</v>
       </c>
       <c r="M13" s="15">
         <f>H13-I13-J13-K13-L13</f>
@@ -4255,23 +4255,23 @@
         <v>2978</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3698</v>
+        <v>3665</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>13588641</v>
+        <v>13932568</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>298950</v>
+        <v>306516</v>
       </c>
       <c r="H14" s="10">
         <f>F14-G14</f>
         <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>6172752</v>
+        <v>6074976</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1899339</v>
@@ -4280,7 +4280,7 @@
         <v>588160</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>730933</v>
+        <v>749433</v>
       </c>
       <c r="M14" s="15">
         <f>H14-I14-J14-K14-L14</f>
@@ -4312,10 +4312,10 @@
         <v>73</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>13965880</v>
+        <v>14550296</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>307249</v>
+        <v>320107</v>
       </c>
       <c r="H15" s="10">
         <f>F15-G15</f>
@@ -4331,7 +4331,7 @@
         <v>588160</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>751225</v>
+        <v>782660</v>
       </c>
       <c r="M15" s="15">
         <f>H15-I15-J15-K15-L15</f>
@@ -4363,10 +4363,10 @@
         <v>73</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>13965880</v>
+        <v>14550296</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>307249</v>
+        <v>320107</v>
       </c>
       <c r="H16" s="10">
         <f>F16-G16</f>
@@ -4382,7 +4382,7 @@
         <v>588160</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>751225</v>
+        <v>782660</v>
       </c>
       <c r="M16" s="15">
         <f>H16-I16-J16-K16-L16</f>
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>47061856</v>
+        <v>48183882</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>5883180</v>
+        <v>7470537</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>8256398</v>
+        <v>8600389</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>2203</v>
@@ -4539,7 +4539,7 @@
         <v>2595</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>24551</v>
+        <v>24144</v>
       </c>
     </row>
     <row r="8">
@@ -4549,13 +4549,13 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>74926660</v>
+        <v>72868799</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>18681568</v>
+        <v>19765357</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>13965880</v>
+        <v>14550296</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>2978</v>
@@ -4564,7 +4564,7 @@
         <v>3756</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>37320</v>
+        <v>34858</v>
       </c>
     </row>
     <row r="9">
@@ -4574,13 +4574,13 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>98853195</v>
+        <v>89285019</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>30704948</v>
+        <v>29026940</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>18952542</v>
+        <v>19653011</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>3476</v>
@@ -4589,7 +4589,7 @@
         <v>4653</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>48363</v>
+        <v>42121</v>
       </c>
     </row>
   </sheetData>
@@ -6049,7 +6049,7 @@
         <v>0.25</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.3595990133326435</v>
+        <v>0.3498662947578072</v>
       </c>
       <c r="D7" s="9">
         <f>C7-B7</f>
@@ -6071,7 +6071,7 @@
         <v>0.05</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.0106360054989733</v>
+        <v>0.01064181335234133</v>
       </c>
       <c r="D8" s="9">
         <f>C8-B8</f>
@@ -6093,7 +6093,7 @@
         <v>0.1</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.01301511918592931</v>
+        <v>0.01310211908740365</v>
       </c>
       <c r="D9" s="9">
         <f>C9-B9</f>
@@ -6115,7 +6115,7 @@
         <v>0.1</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.1158500866047987</v>
+        <v>0.1160396420948</v>
       </c>
       <c r="D10" s="9">
         <f>C10-B10</f>
@@ -6137,7 +6137,7 @@
         <v>0.25</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.2504498876888276</v>
+        <v>0.2551750653538239</v>
       </c>
       <c r="D11" s="9">
         <f>C11-B11</f>
@@ -6159,7 +6159,7 @@
         <v>0.25</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.2504498876888276</v>
+        <v>0.2551750653538239</v>
       </c>
       <c r="D12" s="9">
         <f>C12-B12</f>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>17395110</v>
+        <v>17167004</v>
       </c>
     </row>
     <row r="15">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>8713207</v>
+        <v>8761183</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>0.5008997753776553</v>
+        <v>0.5103501307076479</v>
       </c>
     </row>
     <row r="17">
@@ -6260,28 +6260,28 @@
         <v>0.6</v>
       </c>
       <c r="B21" s="10" t="n">
-        <v>10250</v>
+        <v>10700</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>16750</v>
+        <v>17400</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>30250</v>
+        <v>31450</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>18039853</v>
+        <v>18063477</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>4000</v>
+        <v>3922</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.5495767520971756</v>
+        <v>0.5308051235874529</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.1387561750087432</v>
+        <v>0.1361516943830914</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0.2857462257675683</v>
+        <v>0.3074094509063911</v>
       </c>
     </row>
     <row r="22">
@@ -6289,28 +6289,28 @@
         <v>0.7</v>
       </c>
       <c r="B22" s="10" t="n">
-        <v>11950</v>
+        <v>12450</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>19550</v>
+        <v>20300</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>35300</v>
+        <v>36700</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>18114228</v>
+        <v>18130686</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3690</v>
+        <v>3617</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.4794499741592875</v>
+        <v>0.4641848827686511</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.1285276965708944</v>
+        <v>0.1260267261812377</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>0.3672244946210855</v>
+        <v>0.3852489620488544</v>
       </c>
     </row>
     <row r="23">
@@ -6318,28 +6318,28 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="B23" s="10" t="n">
-        <v>13700</v>
+        <v>14250</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>22300</v>
+        <v>23200</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>40300</v>
+        <v>41900</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>18172602</v>
+        <v>18188105</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>3457</v>
+        <v>3398</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.4289409633204131</v>
+        <v>0.4152978808886788</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.1204675588008806</v>
+        <v>0.1184140403851858</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0.4266349223507077</v>
+        <v>0.4425446361359258</v>
       </c>
     </row>
     <row r="24">
@@ -6347,28 +6347,28 @@
         <v>0.8999999999999999</v>
       </c>
       <c r="B24" s="10" t="n">
-        <v>15400</v>
+        <v>16000</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>25100</v>
+        <v>26100</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>45350</v>
+        <v>47150</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>18026952</v>
+        <v>17795040</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3260</v>
+        <v>3178</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.3897782252626893</v>
+        <v>0.3782320166055471</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.1158619049964742</v>
+        <v>0.1157447805680684</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>0.4708556110295951</v>
+        <v>0.4824863535688792</v>
       </c>
     </row>
     <row r="25">
@@ -6376,28 +6376,28 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="B25" s="15" t="n">
-        <v>17100</v>
+        <v>17800</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>27900</v>
+        <v>29000</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>50400</v>
+        <v>52400</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>17395110</v>
+        <v>17167004</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3053</v>
+        <v>2989</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.3595990133326435</v>
+        <v>0.3498662947578072</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>0.1158500866047987</v>
+        <v>0.1160396420948</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>0.5008997753776553</v>
+        <v>0.5103501307076479</v>
       </c>
     </row>
     <row r="26">
@@ -6405,28 +6405,28 @@
         <v>1.1</v>
       </c>
       <c r="B26" s="10" t="n">
-        <v>18800</v>
+        <v>19600</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>30700</v>
+        <v>31900</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>55450</v>
+        <v>57650</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>16841536</v>
+        <v>16622778</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>2904</v>
+        <v>2854</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.3360145026805764</v>
+        <v>0.327563764605759</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.1164818339609879</v>
+        <v>0.116927146593668</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>0.5236042039905265</v>
+        <v>0.5314773595757852</v>
       </c>
     </row>
     <row r="27">
@@ -6434,28 +6434,28 @@
         <v>1.2</v>
       </c>
       <c r="B27" s="10" t="n">
-        <v>20500</v>
+        <v>21350</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>33500</v>
+        <v>34800</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>60500</v>
+        <v>62900</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>16356111</v>
+        <v>16146982</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>2795</v>
+        <v>2755</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.3173124945999873</v>
+        <v>0.3103293803200739</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.1175803343472051</v>
+        <v>0.1182551017893003</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>0.5408979089702293</v>
+        <v>0.5470325032028865</v>
       </c>
     </row>
     <row r="28">
@@ -6463,28 +6463,28 @@
         <v>1.3</v>
       </c>
       <c r="B28" s="10" t="n">
-        <v>22250</v>
+        <v>23150</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>36250</v>
+        <v>37700</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>65500</v>
+        <v>68100</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>15930220</v>
+        <v>15725619</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>2718</v>
+        <v>2686</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.3032307927276961</v>
+        <v>0.2963525927361231</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.1190714252533863</v>
+        <v>0.1199717480119542</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>0.5531209574204794</v>
+        <v>0.558899950481403</v>
       </c>
     </row>
     <row r="29">
@@ -6492,28 +6492,28 @@
         <v>1.4</v>
       </c>
       <c r="B29" s="10" t="n">
-        <v>23950</v>
+        <v>24900</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>39050</v>
+        <v>40600</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>70550</v>
+        <v>73350</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>15545294</v>
+        <v>15343937</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>2661</v>
+        <v>2637</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.2907002022883821</v>
+        <v>0.2856651939964737</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.1208509147527219</v>
+        <v>0.1219981547108803</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0.5634889496989965</v>
+        <v>0.567134341399779</v>
       </c>
     </row>
     <row r="30">
@@ -6521,28 +6521,28 @@
         <v>1.5</v>
       </c>
       <c r="B30" s="10" t="n">
-        <v>25650</v>
+        <v>26700</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>41850</v>
+        <v>43500</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>75600</v>
+        <v>78600</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>15188128</v>
+        <v>14978948</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>2620</v>
+        <v>2586</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.281012818779319</v>
+        <v>0.2754963318478002</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.1229767091770625</v>
+        <v>0.1237554199400385</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0.5706161100725128</v>
+        <v>0.5751420210158784</v>
       </c>
     </row>
     <row r="31">
@@ -6550,28 +6550,28 @@
         <v>1.6</v>
       </c>
       <c r="B31" s="10" t="n">
-        <v>27350</v>
+        <v>28500</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>44650</v>
+        <v>46400</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>80650</v>
+        <v>83850</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>14840247</v>
+        <v>14629036</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>2560</v>
+        <v>2522</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.2725675734647127</v>
+        <v>0.2675067800501665</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.124124551296215</v>
+        <v>0.124767072826945</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0.5775583916881233</v>
+        <v>0.5817632596593199</v>
       </c>
     </row>
     <row r="32">
@@ -6579,28 +6579,28 @@
         <v>1.7</v>
       </c>
       <c r="B32" s="10" t="n">
-        <v>29050</v>
+        <v>30250</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>47450</v>
+        <v>49300</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>85700</v>
+        <v>89100</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>14514522</v>
+        <v>14307940</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>2502</v>
+        <v>2470</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.2644025437282586</v>
+        <v>0.2600536412572838</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.1251534153174317</v>
+        <v>0.1259378359148836</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>0.5843540756025433</v>
+        <v>0.5876788689548696</v>
       </c>
     </row>
     <row r="33">
@@ -6608,28 +6608,28 @@
         <v>1.8</v>
       </c>
       <c r="B33" s="10" t="n">
-        <v>30800</v>
+        <v>32050</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>50200</v>
+        <v>52200</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>90700</v>
+        <v>94300</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>14213299</v>
+        <v>14008359</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>2455</v>
+        <v>2425</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.2582893333190636</v>
+        <v>0.2545396423693412</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.1263313323669614</v>
+        <v>0.1272652992402608</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0.5889328718224852</v>
+        <v>0.5914846621967186</v>
       </c>
     </row>
     <row r="34">
@@ -6637,28 +6637,28 @@
         <v>1.900000000000001</v>
       </c>
       <c r="B34" s="10" t="n">
-        <v>32500</v>
+        <v>33800</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>53000</v>
+        <v>55100</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>95750</v>
+        <v>99550</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>13931012</v>
+        <v>13729981</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>2415</v>
+        <v>2389</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.2529421094553104</v>
+        <v>0.2488363837448651</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.1276399015376629</v>
+        <v>0.1287054220978165</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>0.592610461018543</v>
+        <v>0.5953706446311234</v>
       </c>
     </row>
     <row r="35">
@@ -6666,28 +6666,28 @@
         <v>2</v>
       </c>
       <c r="B35" s="10" t="n">
-        <v>34200</v>
+        <v>35600</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>55800</v>
+        <v>58000</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>100800</v>
+        <v>104800</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>13666639</v>
+        <v>13467004</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>2381</v>
+        <v>2358</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.2476667265495177</v>
+        <v>0.2446030362826645</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.1290602612683338</v>
+        <v>0.1302771574137796</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>0.5960990360699771</v>
+        <v>0.5976444543873587</v>
       </c>
     </row>
     <row r="36">
@@ -6695,28 +6695,28 @@
         <v>2.100000000000001</v>
       </c>
       <c r="B36" s="10" t="n">
-        <v>35900</v>
+        <v>37400</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>58600</v>
+        <v>60900</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>105850</v>
+        <v>110050</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>13418011</v>
+        <v>13219505</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>2352</v>
+        <v>2332</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.2440138740927893</v>
+        <v>0.2412734936146229</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.1305800092129899</v>
+        <v>0.1319497969099448</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0.5978525796001546</v>
+        <v>0.598899294817463</v>
       </c>
     </row>
     <row r="37">
@@ -6724,28 +6724,28 @@
         <v>2.200000000000001</v>
       </c>
       <c r="B37" s="10" t="n">
-        <v>37600</v>
+        <v>39150</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>61400</v>
+        <v>63800</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>110900</v>
+        <v>115300</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>13183374</v>
+        <v>12987813</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>2328</v>
+        <v>2310</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.2407757297742488</v>
+        <v>0.2378072131592553</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.132188315373591</v>
+        <v>0.1336837079499066</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>0.5991001613150656</v>
+        <v>0.6002395484552473</v>
       </c>
     </row>
     <row r="38">
@@ -6753,28 +6753,28 @@
         <v>2.300000000000001</v>
       </c>
       <c r="B38" s="10" t="n">
-        <v>39350</v>
+        <v>40950</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>64150</v>
+        <v>66700</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>115900</v>
+        <v>120500</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>12961540</v>
+        <v>12766930</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>2308</v>
+        <v>2292</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.2378970404864541</v>
+        <v>0.2361651471011889</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.1338902630397314</v>
+        <v>0.1355209905592026</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0.5998904467390367</v>
+        <v>0.599629680487897</v>
       </c>
     </row>
     <row r="39">
@@ -6782,28 +6782,28 @@
         <v>2.400000000000001</v>
       </c>
       <c r="B39" s="10" t="n">
-        <v>41050</v>
+        <v>42700</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>66950</v>
+        <v>69600</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>120950</v>
+        <v>125750</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>12750526</v>
+        <v>12558464</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>2290</v>
+        <v>2277</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.2356321459870337</v>
+        <v>0.2340951165434026</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.1356503253277551</v>
+        <v>0.1374011981083037</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>0.6000104200055989</v>
+        <v>0.5994190370409147</v>
       </c>
     </row>
     <row r="40">
@@ -6811,28 +6811,28 @@
         <v>2.500000000000001</v>
       </c>
       <c r="B40" s="10" t="n">
-        <v>42750</v>
+        <v>44500</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>69750</v>
+        <v>72500</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>126000</v>
+        <v>131000</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>12549708</v>
+        <v>12358015</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2276</v>
+        <v>2264</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.2343153167408257</v>
+        <v>0.2322354811078013</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.137473796203067</v>
+        <v>0.1393770763346703</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>0.599101212887686</v>
+        <v>0.5988983312585385</v>
       </c>
     </row>
     <row r="41">
@@ -6840,28 +6840,28 @@
         <v>2.600000000000001</v>
       </c>
       <c r="B41" s="10" t="n">
-        <v>44450</v>
+        <v>46300</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>72550</v>
+        <v>75400</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>131050</v>
+        <v>136250</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>12358078</v>
+        <v>12166611</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>2264</v>
+        <v>2254</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.232330409064089</v>
+        <v>0.2308386220713664</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.139355650611689</v>
+        <v>0.1414127566008316</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0.5988201726171776</v>
+        <v>0.5978395315115793</v>
       </c>
     </row>
     <row r="42">
@@ -6869,28 +6869,28 @@
         <v>2.700000000000001</v>
       </c>
       <c r="B42" s="10" t="n">
-        <v>46150</v>
+        <v>48050</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>75350</v>
+        <v>78300</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>136100</v>
+        <v>141500</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>12174805</v>
+        <v>11985341</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>2254</v>
+        <v>2245</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.2306246389309383</v>
+        <v>0.230016208633424</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.1412910514788533</v>
+        <v>0.1434659222461839</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0.598200228564673</v>
+        <v>0.5962010310307209</v>
       </c>
     </row>
     <row r="43">
@@ -6898,28 +6898,28 @@
         <v>2.800000000000001</v>
       </c>
       <c r="B43" s="10" t="n">
-        <v>47900</v>
+        <v>49850</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>78100</v>
+        <v>81200</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>141100</v>
+        <v>146700</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>11999000</v>
+        <v>11810102</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>2246</v>
+        <v>2239</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.2300156995723689</v>
+        <v>0.22937744889824</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.1432993582798567</v>
+        <v>0.145602722144144</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>0.596397664490099</v>
+        <v>0.5942883561836423</v>
       </c>
     </row>
     <row r="44">
@@ -6927,28 +6927,28 @@
         <v>2.900000000000001</v>
       </c>
       <c r="B44" s="10" t="n">
-        <v>49600</v>
+        <v>51600</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>80900</v>
+        <v>84100</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>146150</v>
+        <v>151950</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>11830304</v>
+        <v>11643171</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>2239</v>
+        <v>2233</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.2298273530660217</v>
+        <v>0.2288255599052353</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.1453307539687907</v>
+        <v>0.1477490968740389</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>0.5941528563853372</v>
+        <v>0.5922838770631683</v>
       </c>
     </row>
     <row r="45">
@@ -6956,28 +6956,28 @@
         <v>3.000000000000001</v>
       </c>
       <c r="B45" s="10" t="n">
-        <v>51300</v>
+        <v>53400</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>83700</v>
+        <v>87000</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>151200</v>
+        <v>157200</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>11668095</v>
+        <v>11480754</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.2291900699682136</v>
+        <v>0.2293107301135573</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.1474036678652342</v>
+        <v>0.1499778673073215</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>0.5923211347486614</v>
+        <v>0.5891397295402898</v>
       </c>
     </row>
   </sheetData>

--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>52571072</v>
+        <v>52432994</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>-10611226</v>
+        <v>-10664427</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>15450829</v>
+        <v>15450823</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>5206</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>32147</v>
+        <v>32024</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>63983540</v>
+        <v>63873017</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>5371978</v>
+        <v>5302585</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>16687817</v>
@@ -3727,10 +3727,10 @@
         <v>3812</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>27038</v>
+        <v>27000</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>4140126</v>
+        <v>4140094</v>
       </c>
     </row>
     <row r="9">
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>72868799</v>
+        <v>70457741</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>19765357</v>
+        <v>19117138</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>14550296</v>
@@ -3752,10 +3752,10 @@
         <v>3756</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>34858</v>
+        <v>33401</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>12238554</v>
+        <v>11865837</v>
       </c>
     </row>
   </sheetData>
@@ -3895,35 +3895,35 @@
         <v>2027</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>144281</v>
+        <v>74370</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>3174</v>
+        <v>1636</v>
       </c>
       <c r="H7" s="10">
         <f>F7-G7</f>
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>50590</v>
+        <v>24444</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>45435</v>
+        <v>23794</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>363820</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>7761</v>
+        <v>4000</v>
       </c>
       <c r="M7" s="15">
         <f>H7-I7-J7-K7-L7</f>
@@ -3946,35 +3946,35 @@
         <v>2028</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>241</v>
+        <v>157</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>846035</v>
+        <v>674354</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>18613</v>
+        <v>14836</v>
       </c>
       <c r="H8" s="10">
         <f>F8-G8</f>
         <v/>
       </c>
       <c r="I8" s="10" t="n">
-        <v>319041</v>
+        <v>220343</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>180448</v>
+        <v>130674</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>45508</v>
+        <v>36274</v>
       </c>
       <c r="M8" s="15">
         <f>H8-I8-J8-K8-L8</f>
@@ -3997,35 +3997,35 @@
         <v>2029</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>430</v>
+        <v>365</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>493</v>
+        <v>406</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1770193</v>
+        <v>1742874</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>38944</v>
+        <v>38343</v>
       </c>
       <c r="H9" s="10">
         <f>F9-G9</f>
         <v/>
       </c>
       <c r="I9" s="10" t="n">
-        <v>746999</v>
+        <v>645162</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>274002</v>
+        <v>252084</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>95219</v>
+        <v>93749</v>
       </c>
       <c r="M9" s="15">
         <f>H9-I9-J9-K9-L9</f>
@@ -4048,35 +4048,35 @@
         <v>2030</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>733</v>
+        <v>690</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>845</v>
+        <v>786</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3046745</v>
+        <v>2944069</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>67028</v>
+        <v>64770</v>
       </c>
       <c r="H10" s="10">
         <f>F10-G10</f>
         <v/>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1328516</v>
+        <v>1241187</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>467457</v>
+        <v>440408</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>163884</v>
+        <v>158361</v>
       </c>
       <c r="M10" s="15">
         <f>H10-I10-J10-K10-L10</f>
@@ -4099,35 +4099,35 @@
         <v>2031</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1178</v>
+        <v>1083</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1370</v>
+        <v>1263</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4973433</v>
+        <v>4599805</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>109416</v>
+        <v>101196</v>
       </c>
       <c r="H11" s="10">
         <f>F11-G11</f>
         <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>2168626</v>
+        <v>2005705</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>751686</v>
+        <v>690667</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>267521</v>
+        <v>247424</v>
       </c>
       <c r="M11" s="15">
         <f>H11-I11-J11-K11-L11</f>
@@ -4150,35 +4150,35 @@
         <v>2032</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1795</v>
+        <v>1663</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2103</v>
+        <v>1946</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7684272</v>
+        <v>7103261</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>169054</v>
+        <v>156272</v>
       </c>
       <c r="H12" s="10">
         <f>F12-G12</f>
         <v/>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3350650</v>
+        <v>3097308</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1144808</v>
+        <v>1060607</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>413337</v>
+        <v>382084</v>
       </c>
       <c r="M12" s="15">
         <f>H12-I12-J12-K12-L12</f>
@@ -4201,35 +4201,35 @@
         <v>2033</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2627</v>
+        <v>2452</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>3096</v>
+        <v>2887</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>11370680</v>
+        <v>10593120</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>250155</v>
+        <v>233049</v>
       </c>
       <c r="H13" s="10">
         <f>F13-G13</f>
         <v/>
       </c>
       <c r="I13" s="10" t="n">
-        <v>4958052</v>
+        <v>4619010</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1675680</v>
+        <v>1564428</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>611629</v>
+        <v>569804</v>
       </c>
       <c r="M13" s="15">
         <f>H13-I13-J13-K13-L13</f>
@@ -4255,23 +4255,23 @@
         <v>2978</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3665</v>
+        <v>3619</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>13932568</v>
+        <v>13625296</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>306516</v>
+        <v>299757</v>
       </c>
       <c r="H14" s="10">
         <f>F14-G14</f>
         <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>6074976</v>
+        <v>5941040</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1899339</v>
@@ -4280,7 +4280,7 @@
         <v>588160</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>749433</v>
+        <v>732905</v>
       </c>
       <c r="M14" s="15">
         <f>H14-I14-J14-K14-L14</f>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>48183882</v>
+        <v>46060015</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>7470537</v>
+        <v>7031869</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>8600389</v>
@@ -4539,7 +4539,7 @@
         <v>2595</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>24144</v>
+        <v>22877</v>
       </c>
     </row>
     <row r="8">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>72868799</v>
+        <v>70457741</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>19765357</v>
+        <v>19117138</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>14550296</v>
@@ -4564,7 +4564,7 @@
         <v>3756</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>34858</v>
+        <v>33401</v>
       </c>
     </row>
     <row r="9">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>89285019</v>
+        <v>87839129</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>29026940</v>
+        <v>28705700</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>19653011</v>
@@ -4589,7 +4589,7 @@
         <v>4653</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>42121</v>
+        <v>41058</v>
       </c>
     </row>
   </sheetData>

--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -4574,22 +4574,22 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>87839129</v>
+        <v>81727680</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>28705700</v>
+        <v>26207874</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>19653011</v>
+        <v>17386577</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>3476</v>
+        <v>2978</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>4653</v>
+        <v>3986</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>41058</v>
+        <v>37365</v>
       </c>
     </row>
   </sheetData>

--- a/publication/WEC-LC Financial Model.xlsx
+++ b/publication/WEC-LC Financial Model.xlsx
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>52432994</v>
+        <v>52447185</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>-10664427</v>
+        <v>-10665397</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>15450823</v>
+        <v>15450824</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>5206</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>32024</v>
+        <v>32034</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>63873017</v>
+        <v>63888026</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>5302585</v>
+        <v>5306559</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>16687817</v>
@@ -3727,10 +3727,10 @@
         <v>3812</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>27000</v>
+        <v>27007</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>4140094</v>
+        <v>4140109</v>
       </c>
     </row>
     <row r="9">
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>70457741</v>
+        <v>70466166</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>19117138</v>
+        <v>19119095</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>14550296</v>
@@ -3752,10 +3752,10 @@
         <v>3756</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>33401</v>
+        <v>33409</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>11865837</v>
+        <v>11864298</v>
       </c>
     </row>
   </sheetData>
@@ -3895,35 +3895,35 @@
         <v>2027</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>74370</v>
+        <v>90676</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1636</v>
+        <v>1995</v>
       </c>
       <c r="H7" s="10">
         <f>F7-G7</f>
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>24444</v>
+        <v>29804</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>23794</v>
+        <v>29011</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>363820</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>4000</v>
+        <v>4877</v>
       </c>
       <c r="M7" s="15">
         <f>H7-I7-J7-K7-L7</f>
@@ -3946,35 +3946,35 @@
         <v>2028</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>674354</v>
+        <v>669614</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>14836</v>
+        <v>14732</v>
       </c>
       <c r="H8" s="10">
         <f>F8-G8</f>
         <v/>
       </c>
       <c r="I8" s="10" t="n">
-        <v>220343</v>
+        <v>218725</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>130674</v>
+        <v>127883</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>36274</v>
+        <v>36019</v>
       </c>
       <c r="M8" s="15">
         <f>H8-I8-J8-K8-L8</f>
@@ -3997,7 +3997,7 @@
         <v>2029</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>406</v>
@@ -4006,26 +4006,26 @@
         <v>8</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1742874</v>
+        <v>1738927</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>38343</v>
+        <v>38256</v>
       </c>
       <c r="H9" s="10">
         <f>F9-G9</f>
         <v/>
       </c>
       <c r="I9" s="10" t="n">
-        <v>645162</v>
+        <v>644084</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>252084</v>
+        <v>252751</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>93749</v>
+        <v>93537</v>
       </c>
       <c r="M9" s="15">
         <f>H9-I9-J9-K9-L9</f>
@@ -4057,26 +4057,26 @@
         <v>15</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2944069</v>
+        <v>2944998</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>64770</v>
+        <v>64790</v>
       </c>
       <c r="H10" s="10">
         <f>F10-G10</f>
         <v/>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1241187</v>
+        <v>1241479</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>440408</v>
+        <v>440173</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>158361</v>
+        <v>158411</v>
       </c>
       <c r="M10" s="15">
         <f>H10-I10-J10-K10-L10</f>
@@ -4108,26 +4108,26 @@
         <v>24</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4599805</v>
+        <v>4599627</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>101196</v>
+        <v>101192</v>
       </c>
       <c r="H11" s="10">
         <f>F11-G11</f>
         <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>2005705</v>
+        <v>2005627</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>690667</v>
+        <v>690763</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>247424</v>
+        <v>247414</v>
       </c>
       <c r="M11" s="15">
         <f>H11-I11-J11-K11-L11</f>
@@ -4159,26 +4159,26 @@
         <v>37</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7103261</v>
+        <v>7103354</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>156272</v>
+        <v>156274</v>
       </c>
       <c r="H12" s="10">
         <f>F12-G12</f>
         <v/>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3097308</v>
+        <v>3097349</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1060607</v>
+        <v>1060572</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>382084</v>
+        <v>382089</v>
       </c>
       <c r="M12" s="15">
         <f>H12-I12-J12-K12-L12</f>
@@ -4210,26 +4210,26 @@
         <v>55</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>10593120</v>
+        <v>10593061</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>233049</v>
+        <v>233047</v>
       </c>
       <c r="H13" s="10">
         <f>F13-G13</f>
         <v/>
       </c>
       <c r="I13" s="10" t="n">
-        <v>4619010</v>
+        <v>4618983</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1564428</v>
+        <v>1564436</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>588160</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>569804</v>
+        <v>569801</v>
       </c>
       <c r="M13" s="15">
         <f>H13-I13-J13-K13-L13</f>
@@ -4261,7 +4261,7 @@
         <v>70</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>13625296</v>
+        <v>13625317</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>299757</v>
@@ -4271,7 +4271,7 @@
         <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>5941040</v>
+        <v>5941050</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1899339</v>
@@ -4280,7 +4280,7 @@
         <v>588160</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>732905</v>
+        <v>732906</v>
       </c>
       <c r="M14" s="15">
         <f>H14-I14-J14-K14-L14</f>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46060015</v>
+        <v>46034028</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>7031869</v>
+        <v>7020614</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>8600389</v>
@@ -4539,7 +4539,7 @@
         <v>2595</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>22877</v>
+        <v>22869</v>
       </c>
     </row>
     <row r="8">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>70457741</v>
+        <v>70466166</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>19117138</v>
+        <v>19119095</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>14550296</v>
@@ -4564,7 +4564,7 @@
         <v>3756</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>33401</v>
+        <v>33409</v>
       </c>
     </row>
     <row r="9">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>81727680</v>
+        <v>81742316</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>26207874</v>
+        <v>26213017</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>17386577</v>
@@ -4589,7 +4589,7 @@
         <v>3986</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>37365</v>
+        <v>37379</v>
       </c>
     </row>
   </sheetData>
